--- a/docs/downloads/11/tbl_cata_type_alaotra_tous.xlsx
+++ b/docs/downloads/11/tbl_cata_type_alaotra_tous.xlsx
@@ -441,12 +441,6 @@
           <t>Maladie des cultures/élevage</t>
         </is>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>12.9</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -459,12 +453,6 @@
           <t>Facteur humain</t>
         </is>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>9.699999999999999</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -477,12 +465,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -495,12 +477,6 @@
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -585,12 +561,6 @@
           <t>Autres bestioles</t>
         </is>
       </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>5.9</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -603,12 +573,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>2.9</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -621,12 +585,6 @@
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -639,12 +597,6 @@
           <t>Oiseaux</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -747,12 +699,6 @@
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22">
-        <v>5.2</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -765,12 +711,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -783,12 +723,6 @@
           <t>Inondation</t>
         </is>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -891,12 +825,6 @@
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -909,12 +837,6 @@
           <t>Grêle</t>
         </is>
       </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -981,12 +903,6 @@
           <t>Rats</t>
         </is>
       </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-      <c r="D35">
-        <v>8.699999999999999</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -999,12 +915,6 @@
           <t>Inondation</t>
         </is>
       </c>
-      <c r="C36">
-        <v>3</v>
-      </c>
-      <c r="D36">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1017,12 +927,6 @@
           <t>Maladie des cultures/élevage</t>
         </is>
       </c>
-      <c r="C37">
-        <v>3</v>
-      </c>
-      <c r="D37">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1179,12 +1083,6 @@
           <t>Incendie / Foudre</t>
         </is>
       </c>
-      <c r="C46">
-        <v>4</v>
-      </c>
-      <c r="D46">
-        <v>4.4</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1197,12 +1095,6 @@
           <t>Criquets</t>
         </is>
       </c>
-      <c r="C47">
-        <v>2</v>
-      </c>
-      <c r="D47">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1215,12 +1107,6 @@
           <t>Oiseaux</t>
         </is>
       </c>
-      <c r="C48">
-        <v>2</v>
-      </c>
-      <c r="D48">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1233,12 +1119,6 @@
           <t>Grêle</t>
         </is>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1359,12 +1239,6 @@
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C56">
-        <v>2</v>
-      </c>
-      <c r="D56">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1377,12 +1251,6 @@
           <t>Grêle</t>
         </is>
       </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1485,12 +1353,6 @@
           <t>Grêle</t>
         </is>
       </c>
-      <c r="C63">
-        <v>4</v>
-      </c>
-      <c r="D63">
-        <v>5.5</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1503,12 +1365,6 @@
           <t>Maladie des cultures/élevage</t>
         </is>
       </c>
-      <c r="C64">
-        <v>4</v>
-      </c>
-      <c r="D64">
-        <v>5.5</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1521,12 +1377,6 @@
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C65">
-        <v>1</v>
-      </c>
-      <c r="D65">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1539,12 +1389,6 @@
           <t>Oiseaux</t>
         </is>
       </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-      <c r="D66">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1719,12 +1563,6 @@
           <t>Incendie / Foudre</t>
         </is>
       </c>
-      <c r="C76">
-        <v>4</v>
-      </c>
-      <c r="D76">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1737,12 +1575,6 @@
           <t>Oiseaux</t>
         </is>
       </c>
-      <c r="C77">
-        <v>4</v>
-      </c>
-      <c r="D77">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1754,12 +1586,6 @@
         <is>
           <t>Criquets</t>
         </is>
-      </c>
-      <c r="C78">
-        <v>2</v>
-      </c>
-      <c r="D78">
-        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/11/tbl_cata_type_alaotra_tous.xlsx
+++ b/docs/downloads/11/tbl_cata_type_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -457,7 +457,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -907,7 +907,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -967,7 +967,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1075,7 +1075,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1111,7 +1111,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1213,7 +1213,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1231,7 +1231,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1243,7 +1243,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1327,7 +1327,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1345,7 +1345,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1405,13 +1405,13 @@
         <v>286</v>
       </c>
       <c r="D67">
-        <v>56.4</v>
+        <v>922.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1423,13 +1423,13 @@
         <v>77</v>
       </c>
       <c r="D68">
-        <v>15.2</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1441,13 +1441,13 @@
         <v>68</v>
       </c>
       <c r="D69">
-        <v>13.4</v>
+        <v>147.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1459,13 +1459,13 @@
         <v>66</v>
       </c>
       <c r="D70">
-        <v>13</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1477,13 +1477,13 @@
         <v>66</v>
       </c>
       <c r="D71">
-        <v>13</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1495,13 +1495,13 @@
         <v>48</v>
       </c>
       <c r="D72">
-        <v>9.5</v>
+        <v>104.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1513,13 +1513,13 @@
         <v>28</v>
       </c>
       <c r="D73">
-        <v>5.5</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1531,13 +1531,13 @@
         <v>11</v>
       </c>
       <c r="D74">
-        <v>2.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1549,13 +1549,13 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>1.4</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1567,7 +1567,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
